--- a/03 - Atrib LONPC No Cor.xlsx
+++ b/03 - Atrib LONPC No Cor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Associação\Atribuições Cargos\Tabelas de Atribuições\3 - Atrib LONPC sem correções\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maiap\OneDrive\Desktop\Desenvolvimento\Estudo_Atribuicoes_PCSP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18AAE36-16E3-4058-A8F0-BE9175A3EBC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EACFAD1-79DA-481F-8E10-A2DAC7939B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9E2F6A9B-94A3-41DD-92E9-2C4405031CDE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{9E2F6A9B-94A3-41DD-92E9-2C4405031CDE}"/>
   </bookViews>
   <sheets>
     <sheet name="LONPC no cor" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>mediar conflitos</t>
   </si>
@@ -197,36 +197,6 @@
   </si>
   <si>
     <t>Médico Legista</t>
-  </si>
-  <si>
-    <t>portar arma, distintivo e algemas</t>
-  </si>
-  <si>
-    <t>atender sempre, com urbanidade e eficiência, o público em geral, pessoalmente ou por telefone</t>
-  </si>
-  <si>
-    <t>elaborar, sob orientação da Autoridade Policial, registro de ocorrência</t>
-  </si>
-  <si>
-    <t>conduzir viatura policial</t>
-  </si>
-  <si>
-    <t>cumprir diligência e/ou requisição determinada pela Autoridade Policial, elaborando relatório respectivo</t>
-  </si>
-  <si>
-    <t>proceder à abordagem de pessoas suspeitas da prática de ilícitos, realizando busca pessoal quando necessário</t>
-  </si>
-  <si>
-    <t>identificar pessoas, inclusive por meio digital, nas hipóteses em que tal providência se faça necessária</t>
-  </si>
-  <si>
-    <t>conduzir e apresentar pessoas legalmente presas à Autoridade Policial competente ou onde for por ela determinado</t>
-  </si>
-  <si>
-    <t>auxiliar a Autoridade Policial na formalização de atos de polícia judiciária</t>
-  </si>
-  <si>
-    <t>operar os sistemas de comunicação e de dados da Polícia Civil</t>
   </si>
   <si>
     <t>gestão de polícia judiciária</t>
@@ -1168,62 +1138,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61E66DEB-712A-465C-882E-F5424BC162B6}">
-  <dimension ref="A1:BU9"/>
+  <dimension ref="A1:BK9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="31.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.44140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="43" max="46" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="55" max="56" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="8" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="69" max="71" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="36" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="8" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="59" max="61" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" s="1" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:63" s="1" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>59</v>
@@ -1235,214 +1195,184 @@
         <v>61</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="N1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T1" s="3" t="s">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="BF1" s="3" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="BI1" s="3" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="BL1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="BM1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="BN1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="BO1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="BP1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="BQ1" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="BR1" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="BS1" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="BT1" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="BU1" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>56</v>
       </c>
@@ -1459,34 +1389,34 @@
         <v>1</v>
       </c>
       <c r="F2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="5">
         <v>0</v>
@@ -1632,52 +1562,22 @@
       <c r="BK2" s="5">
         <v>0</v>
       </c>
-      <c r="BL2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT2" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU2" s="5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="5">
         <v>1</v>
@@ -1698,49 +1598,49 @@
         <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="5">
         <v>1</v>
       </c>
       <c r="Q3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="5">
         <v>0</v>
@@ -1853,70 +1753,40 @@
       <c r="BK3" s="5">
         <v>0</v>
       </c>
-      <c r="BL3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT3" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU3" s="5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>57</v>
       </c>
       <c r="B4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
         <v>0</v>
@@ -1934,34 +1804,34 @@
         <v>0</v>
       </c>
       <c r="Q4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" s="5">
         <v>1</v>
@@ -1979,34 +1849,34 @@
         <v>1</v>
       </c>
       <c r="AF4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP4" s="5">
         <v>0</v>
@@ -2074,70 +1944,40 @@
       <c r="BK4" s="5">
         <v>0</v>
       </c>
-      <c r="BL4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT4" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU4" s="5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>58</v>
       </c>
       <c r="B5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -2167,13 +2007,13 @@
         <v>0</v>
       </c>
       <c r="U5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" s="5">
         <v>0</v>
       </c>
       <c r="W5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" s="5">
         <v>0</v>
@@ -2188,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="AB5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5" s="5">
         <v>0</v>
@@ -2197,19 +2037,19 @@
         <v>0</v>
       </c>
       <c r="AE5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" s="5">
         <v>1</v>
       </c>
       <c r="AH5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" s="5">
         <v>0</v>
@@ -2218,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="AL5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM5" s="5">
         <v>0</v>
@@ -2230,16 +2070,16 @@
         <v>0</v>
       </c>
       <c r="AP5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT5" s="5">
         <v>0</v>
@@ -2295,70 +2135,40 @@
       <c r="BK5" s="5">
         <v>0</v>
       </c>
-      <c r="BL5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT5" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU5" s="5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="5">
         <v>0</v>
@@ -2382,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" s="5">
         <v>0</v>
@@ -2433,28 +2243,28 @@
         <v>0</v>
       </c>
       <c r="AJ6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM6" s="5">
         <v>1</v>
       </c>
       <c r="AN6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR6" s="5">
         <v>0</v>
@@ -2463,28 +2273,28 @@
         <v>0</v>
       </c>
       <c r="AT6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB6" s="5">
         <v>0</v>
@@ -2516,70 +2326,40 @@
       <c r="BK6" s="5">
         <v>0</v>
       </c>
-      <c r="BL6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT6" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU6" s="5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
         <v>0</v>
@@ -2603,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="S7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" s="5">
         <v>0</v>
@@ -2663,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="AM7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN7" s="5">
         <v>0</v>
@@ -2678,13 +2458,13 @@
         <v>0</v>
       </c>
       <c r="AR7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7" s="5">
         <v>0</v>
@@ -2708,13 +2488,13 @@
         <v>0</v>
       </c>
       <c r="BB7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE7" s="5">
         <v>0</v>
@@ -2737,70 +2517,40 @@
       <c r="BK7" s="5">
         <v>0</v>
       </c>
-      <c r="BL7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT7" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU7" s="5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="5">
         <v>0</v>
@@ -2836,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="W8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" s="5">
         <v>0</v>
@@ -2866,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="AG8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" s="5">
         <v>0</v>
@@ -2908,25 +2658,25 @@
         <v>0</v>
       </c>
       <c r="AU8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB8" s="5">
         <v>0</v>
@@ -2938,90 +2688,60 @@
         <v>0</v>
       </c>
       <c r="BE8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK8" s="5">
-        <v>1</v>
-      </c>
-      <c r="BL8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BM8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BN8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BO8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BP8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BQ8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BR8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BS8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BT8" s="5">
-        <v>0</v>
-      </c>
-      <c r="BU8" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:73" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:63" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
         <v>0</v>
@@ -3072,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="AB9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC9" s="5">
         <v>0</v>
@@ -3102,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="AL9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM9" s="5">
         <v>0</v>
@@ -3150,68 +2870,38 @@
         <v>0</v>
       </c>
       <c r="BB9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK9" s="5">
-        <v>0</v>
-      </c>
-      <c r="BL9" s="5">
-        <v>1</v>
-      </c>
-      <c r="BM9" s="5">
-        <v>1</v>
-      </c>
-      <c r="BN9" s="5">
-        <v>1</v>
-      </c>
-      <c r="BO9" s="5">
-        <v>1</v>
-      </c>
-      <c r="BP9" s="5">
-        <v>1</v>
-      </c>
-      <c r="BQ9" s="5">
-        <v>1</v>
-      </c>
-      <c r="BR9" s="5">
-        <v>1</v>
-      </c>
-      <c r="BS9" s="5">
-        <v>1</v>
-      </c>
-      <c r="BT9" s="5">
-        <v>1</v>
-      </c>
-      <c r="BU9" s="5">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:BU9">
+  <conditionalFormatting sqref="B2:BK9">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
